--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486466_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486466_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.993399999999999</v>
+        <v>9.4252</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6625</v>
+        <v>8.4642</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3309</v>
+        <v>0.961</v>
       </c>
       <c r="G2" t="n">
         <v>6.3157</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3084</v>
+        <v>0.7402</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8172</v>
+        <v>0.6189</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4912</v>
+        <v>0.1214</v>
       </c>
       <c r="V2" t="n">
         <v>2.8042</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3639</v>
+        <v>3.3515</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0956</v>
+        <v>4.0523</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7317</v>
+        <v>-0.7009</v>
       </c>
       <c r="G3" t="n">
         <v>1.7283</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2006</v>
+        <v>1.1882</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1032</v>
+        <v>1.0599</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0974</v>
+        <v>0.1283</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.826</v>
+        <v>3.1678</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5832</v>
+        <v>2.9752</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2429</v>
+        <v>0.1926</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2298</v>
+        <v>3.7384</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3739</v>
+        <v>1.4355</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8559</v>
+        <v>2.3029</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3861</v>
+        <v>4.1777</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1277</v>
+        <v>1.9193</v>
       </c>
       <c r="L4" t="n">
         <v>2.2583</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1563</v>
+        <v>-0.4392</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2461</v>
+        <v>-0.4838</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4024</v>
+        <v>0.0446</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0737</v>
+        <v>0.0171</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1971</v>
+        <v>0.0601</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8766</v>
+        <v>-0.043</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.13</v>
+        <v>0.9347</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7602</v>
+        <v>2.6124</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9067</v>
+        <v>2.8319</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1464</v>
+        <v>-0.2195</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7384</v>
+        <v>2.2298</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4355</v>
+        <v>0.3739</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3029</v>
+        <v>1.8559</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1777</v>
+        <v>2.3861</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9193</v>
+        <v>0.1277</v>
       </c>
       <c r="L5" t="n">
         <v>2.2583</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4392</v>
+        <v>-0.1563</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4838</v>
+        <v>0.2461</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0446</v>
+        <v>-0.4024</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3904</v>
+        <v>0.8601</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.4458</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.382</v>
+        <v>0.4143</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9347</v>
+        <v>-1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1463</v>
+        <v>2.2571</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0258</v>
+        <v>3.9825</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8795</v>
+        <v>-1.7254</v>
       </c>
       <c r="G6" t="n">
         <v>1.7431</v>
@@ -922,13 +922,13 @@
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3803</v>
+        <v>0.4912</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8051</v>
+        <v>0.7619</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4248</v>
+        <v>-0.2707</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4997</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2081</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.853</v>
+        <v>-0.7099</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0612</v>
+        <v>0.7178</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6476</v>
+        <v>-1.99</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0524</v>
+        <v>-2.1503</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4048</v>
+        <v>0.1602</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9864000000000001</v>
+        <v>-1.8688</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1378</v>
+        <v>-1.8154</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1514</v>
+        <v>-0.0533</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3388</v>
+        <v>-0.1213</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0854</v>
+        <v>-0.3348</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2534</v>
+        <v>0.2136</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4694</v>
+        <v>-0.4371</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1717</v>
+        <v>0.2464</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2978</v>
+        <v>-0.6835</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8902</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5793</v>
+        <v>-0.4367</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0349</v>
+        <v>0.0769</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5444</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0.4877</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0205</v>
+        <v>0.1631</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.1118</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>I. PONS PONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0587</v>
+        <v>-1.0999</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5607</v>
+        <v>-1.1178</v>
       </c>
       <c r="F9" t="n">
-        <v>0.502</v>
+        <v>0.0179</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.99</v>
+        <v>0.1538</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1503</v>
+        <v>0.1155</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1602</v>
+        <v>0.0382</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8688</v>
+        <v>0.0382</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.8154</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0533</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1213</v>
+        <v>0.1155</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3348</v>
+        <v>0.1155</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2136</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5037</v>
+        <v>-0.1661</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6044</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8992</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. PONS PONS</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1307</v>
+        <v>-1.1368</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1178</v>
+        <v>0.2942</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0129</v>
+        <v>-1.431</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1538</v>
+        <v>0.6476</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1155</v>
+        <v>1.0524</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0382</v>
+        <v>-0.4048</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0382</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1.1378</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0382</v>
+        <v>-0.1514</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1155</v>
+        <v>-0.3388</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1155</v>
+        <v>-0.0854</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.2534</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.197</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.6129</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1285</v>
+        <v>-0.0721</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3214</v>
+        <v>-1.4977</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9042</v>
+        <v>-0.3886</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4173</v>
+        <v>-1.109</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3149</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7895</v>
+        <v>0.0342</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3184</v>
+        <v>0.1971</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4711</v>
+        <v>-0.1628</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3045</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.525</v>
+        <v>-2.7802</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7201</v>
+        <v>-2.0986</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.6816</v>
       </c>
       <c r="G12" t="n">
         <v>0.6636</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3117</v>
+        <v>0.0565</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4831</v>
+        <v>0.1046</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1714</v>
+        <v>-0.0481</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3252</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.128</v>
+        <v>-3.047</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8056</v>
+        <v>-0.6939</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3223</v>
+        <v>-2.3532</v>
       </c>
       <c r="G13" t="n">
         <v>0.4865</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0359</v>
+        <v>0.1169</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0565</v>
+        <v>0.0553</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0924</v>
+        <v>0.0616</v>
       </c>
       <c r="V13" t="n">
         <v>-3.2154</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1386</v>
+        <v>10.8236</v>
       </c>
       <c r="E14" t="n">
-        <v>16.9835</v>
+        <v>17.6684</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.844799999999999</v>
+        <v>-6.8449</v>
       </c>
       <c r="G14" t="n">
         <v>14.8896</v>
       </c>
       <c r="H14" t="n">
-        <v>5.550100000000001</v>
+        <v>5.5501</v>
       </c>
       <c r="I14" t="n">
         <v>9.339300000000001</v>
@@ -1522,7 +1522,7 @@
         <v>19.1897</v>
       </c>
       <c r="K14" t="n">
-        <v>6.5713</v>
+        <v>6.571300000000001</v>
       </c>
       <c r="L14" t="n">
         <v>12.6184</v>
@@ -1546,13 +1546,13 @@
         <v>9.7875</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9199</v>
+        <v>3.6051</v>
       </c>
       <c r="T14" t="n">
-        <v>3.521199999999999</v>
+        <v>4.206199999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6010999999999999</v>
+        <v>-0.6008</v>
       </c>
       <c r="V14" t="n">
         <v>-5.4961</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3566</v>
+        <v>1.6524</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1173</v>
+        <v>2.0354</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7606</v>
+        <v>-0.383</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4348</v>
+        <v>-1.252</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1472</v>
+        <v>0.1003</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7124</v>
+        <v>-1.3523</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9697</v>
+        <v>1.2511</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2812</v>
+        <v>1.0981</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6885</v>
+        <v>0.153</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5348</v>
+        <v>-2.5031</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1339</v>
+        <v>-0.9978</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4009</v>
+        <v>-1.5053</v>
       </c>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>0.87</v>
+        <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1817</v>
+        <v>-0.6606</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1476</v>
+        <v>-0.3881</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0341</v>
+        <v>-0.2725</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1877</v>
+        <v>1.4908</v>
       </c>
       <c r="E16" t="n">
         <v>1.5526</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3649</v>
+        <v>-0.0618</v>
       </c>
       <c r="G16" t="n">
         <v>-4.093</v>
@@ -1702,13 +1702,13 @@
         <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8923</v>
+        <v>-0.5891</v>
       </c>
       <c r="T16" t="n">
         <v>0.08409999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9764</v>
+        <v>-0.6733</v>
       </c>
       <c r="V16" t="n">
         <v>3.7804</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8264</v>
+        <v>1.3894</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4766</v>
+        <v>3.335</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6502</v>
+        <v>-1.9456</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.252</v>
+        <v>1.4348</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1003</v>
+        <v>2.1472</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3523</v>
+        <v>-0.7124</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2511</v>
+        <v>2.9697</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0981</v>
+        <v>2.2812</v>
       </c>
       <c r="L17" t="n">
-        <v>0.153</v>
+        <v>0.6885</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5031</v>
+        <v>-1.5348</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9978</v>
+        <v>-0.1339</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5053</v>
+        <v>-1.4009</v>
       </c>
       <c r="P17" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4866</v>
+        <v>0.2145</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9469</v>
+        <v>0.3653</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5397</v>
+        <v>-0.1508</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2599</v>
+        <v>-1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ROBERTS</t>
+          <t>D. SANADZE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3707</v>
+        <v>0.6357</v>
       </c>
       <c r="E18" t="n">
-        <v>1.357</v>
+        <v>1.7693</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9863</v>
+        <v>-1.1336</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2767</v>
+        <v>-1.4239</v>
       </c>
       <c r="H18" t="n">
-        <v>0.003</v>
+        <v>-2.451</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2797</v>
+        <v>1.0271</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6222</v>
+        <v>0.8793</v>
       </c>
       <c r="K18" t="n">
-        <v>0.584</v>
+        <v>-1.5687</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0382</v>
+        <v>2.448</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8989</v>
+        <v>-2.3031</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.581</v>
+        <v>-0.8823</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.318</v>
+        <v>-1.4208</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4522</v>
+        <v>-0.8529</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5396</v>
+        <v>-0.2824</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.5705</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1952</v>
+        <v>2.2599</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>2.2599</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. SANADZE</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0785</v>
+        <v>0.0403</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3223</v>
+        <v>0.9628</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4008</v>
+        <v>-0.9225</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4239</v>
+        <v>-1.566</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.451</v>
+        <v>-0.1492</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0271</v>
+        <v>-1.4168</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8793</v>
+        <v>0.5362</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5687</v>
+        <v>0.3832</v>
       </c>
       <c r="L19" t="n">
-        <v>2.448</v>
+        <v>0.153</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3031</v>
+        <v>-2.1022</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8823</v>
+        <v>-0.5324</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4208</v>
+        <v>-1.5698</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5671</v>
+        <v>0.3665</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7294</v>
+        <v>0.4266</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8377</v>
+        <v>-0.0601</v>
       </c>
       <c r="V19" t="n">
-        <v>2.2599</v>
+        <v>0.3698</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>J. ROBERTS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1087</v>
+        <v>0.0162</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9628</v>
+        <v>0.91</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0715</v>
+        <v>-0.8938</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.566</v>
+        <v>-0.2767</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1492</v>
+        <v>0.003</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4168</v>
+        <v>-0.2797</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5362</v>
+        <v>0.6222</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3832</v>
+        <v>0.584</v>
       </c>
       <c r="L20" t="n">
-        <v>0.153</v>
+        <v>0.0382</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1022</v>
+        <v>-0.8989</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5324</v>
+        <v>-0.581</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5698</v>
+        <v>-0.318</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2175</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4266</v>
+        <v>0.0925</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2091</v>
+        <v>0.0051</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3698</v>
+        <v>0.1952</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5868</v>
+        <v>-0.1103</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0061</v>
+        <v>1.1178</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5929</v>
+        <v>-1.2281</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7749</v>
@@ -2092,13 +2092,13 @@
         <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0496</v>
+        <v>0.4269</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1406</v>
+        <v>0.2524</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1902</v>
+        <v>0.1745</v>
       </c>
       <c r="V21" t="n">
         <v>1.8902</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7815</v>
+        <v>-2.5695</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0285</v>
+        <v>-1.6932</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.753</v>
+        <v>-0.8763</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3942</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6903</v>
+        <v>-0.4783</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0738</v>
+        <v>-0.1971</v>
       </c>
       <c r="V22" t="n">
         <v>0.3904</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0329</v>
+        <v>-5.0509</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4405</v>
+        <v>-0.664</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.5924</v>
+        <v>-4.3869</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6048</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4419</v>
+        <v>0.4239</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4951</v>
+        <v>0.2716</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0532</v>
+        <v>0.1523</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2914</v>
+        <v>-6.1424</v>
       </c>
       <c r="E24" t="n">
         <v>-2.4808</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8107</v>
+        <v>-3.6616</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9389</v>
@@ -2326,13 +2326,13 @@
         <v>1.7401</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5275</v>
+        <v>-0.3785</v>
       </c>
       <c r="T24" t="n">
         <v>0.0601</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5876</v>
+        <v>-0.4386</v>
       </c>
       <c r="V24" t="n">
         <v>-3.3899</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.1384</v>
+        <v>-8.648300000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>6.844899999999997</v>
+        <v>6.844899999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.9833</v>
+        <v>-15.4932</v>
       </c>
       <c r="G25" t="n">
         <v>-14.8896</v>
@@ -2374,7 +2374,7 @@
         <v>-5.550299999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-9.3392</v>
+        <v>-9.339200000000002</v>
       </c>
       <c r="J25" t="n">
         <v>4.3002</v>
@@ -2383,13 +2383,13 @@
         <v>1.0211</v>
       </c>
       <c r="L25" t="n">
-        <v>3.2791</v>
+        <v>3.279099999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-19.1897</v>
       </c>
       <c r="N25" t="n">
-        <v>-6.571300000000001</v>
+        <v>-6.5713</v>
       </c>
       <c r="O25" t="n">
         <v>-12.6185</v>
@@ -2404,13 +2404,13 @@
         <v>11.9629</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.9201</v>
+        <v>-1.43</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6008999999999999</v>
+        <v>0.6009000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.521</v>
+        <v>-2.031</v>
       </c>
       <c r="V25" t="n">
         <v>5.4959</v>
